--- a/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton_Prod.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton_Prod.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="31">
   <si>
     <t>Result</t>
   </si>
@@ -120,6 +120,15 @@
   </si>
   <si>
     <t>Thu Jul 09 11:10:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:18:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:18:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:19:23 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -592,7 +601,7 @@
         <v>19</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
@@ -608,7 +617,7 @@
         <v>19</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>10</v>
@@ -626,7 +635,7 @@
         <v>19</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
